--- a/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T14:19:51+00:00</t>
+    <t>2026-04-07T14:45:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="114">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T14:45:49+00:00</t>
+    <t>2026-04-08T10:07:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -367,12 +367,6 @@
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
 La partie en minuscules indique le code de la langue utilisée (ISO-639-1)
 La partie en majuscules indique le code pays (ISO-3166)</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.code</t>
-  </si>
-  <si>
-    <t>Type de l'entrée</t>
   </si>
 </sst>
 </file>
@@ -674,7 +668,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ16"/>
+  <dimension ref="A1:AJ15"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="38.97265625" customWidth="true" bestFit="true"/>
@@ -2224,106 +2218,6 @@
         <v>73</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="C16" s="2"/>
-      <c r="D16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E16" s="2"/>
-      <c r="F16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K16" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="L16" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="M16" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="AG16" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH16" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI16" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ16" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-entry.xlsx
+++ b/modeleLogiqueSBM/ig/StructureDefinition-fr-lm-entry.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T10:07:24+00:00</t>
+    <t>2026-04-08T12:33:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
